--- a/postcheck.xlsx
+++ b/postcheck.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/srivatsan/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/srivatsan/Desktop/ai-consulting-platform/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C2DB43-34AD-EF44-9230-8E528D107EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F661FB9-6385-8345-B6FB-8CB5014672CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="16640" activeTab="4" xr2:uid="{706BB7B9-90F1-D04B-AFED-02F89A0AB2A0}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="940" windowWidth="30240" windowHeight="16640" activeTab="2" xr2:uid="{706BB7B9-90F1-D04B-AFED-02F89A0AB2A0}"/>
   </bookViews>
   <sheets>
     <sheet name="saas(missing)" sheetId="2" r:id="rId1"/>

--- a/postcheck.xlsx
+++ b/postcheck.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/srivatsan/Desktop/ai-consulting-platform/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F661FB9-6385-8345-B6FB-8CB5014672CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCABE3F-92D5-3E41-9056-CF9E5004E0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="940" windowWidth="30240" windowHeight="16640" activeTab="2" xr2:uid="{706BB7B9-90F1-D04B-AFED-02F89A0AB2A0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="4" xr2:uid="{706BB7B9-90F1-D04B-AFED-02F89A0AB2A0}"/>
   </bookViews>
   <sheets>
     <sheet name="saas(missing)" sheetId="2" r:id="rId1"/>
     <sheet name="saas(partial)" sheetId="3" r:id="rId2"/>
     <sheet name="saas(done)" sheetId="4" r:id="rId3"/>
     <sheet name="orginal" sheetId="5" r:id="rId4"/>
-    <sheet name="postman" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
+    <sheet name="postman" sheetId="1" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="430">
   <si>
     <t>Module</t>
   </si>
@@ -770,9 +771,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>fail</t>
-  </si>
-  <si>
     <t xml:space="preserve">no </t>
   </si>
   <si>
@@ -1278,6 +1276,114 @@
   </si>
   <si>
     <t>White-label Configuration</t>
+  </si>
+  <si>
+    <t>Fail(401 unauthoried)</t>
+  </si>
+  <si>
+    <t>Fail(400)</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>/password-reset/request/</t>
+  </si>
+  <si>
+    <t>/password-reset/verify-otp/</t>
+  </si>
+  <si>
+    <t>/password-reset/confirm/</t>
+  </si>
+  <si>
+    <t>/departments/</t>
+  </si>
+  <si>
+    <t>/teams/</t>
+  </si>
+  <si>
+    <t>/ai-engine/</t>
+  </si>
+  <si>
+    <t>/chat/</t>
+  </si>
+  <si>
+    <t>/architecture/</t>
+  </si>
+  <si>
+    <t>/security/</t>
+  </si>
+  <si>
+    <t>/monitoring/</t>
+  </si>
+  <si>
+    <t>/dashboard/</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>16–19</t>
+  </si>
+  <si>
+    <t>Various</t>
+  </si>
+  <si>
+    <t>21–25</t>
+  </si>
+  <si>
+    <t>26–31</t>
+  </si>
+  <si>
+    <t>32–37</t>
+  </si>
+  <si>
+    <t>38–43</t>
+  </si>
+  <si>
+    <t>46–59</t>
+  </si>
+  <si>
+    <t>64–72</t>
+  </si>
+  <si>
+    <t>74–77</t>
+  </si>
+  <si>
+    <t>80–81</t>
+  </si>
+  <si>
+    <t>82–83</t>
+  </si>
+  <si>
+    <t>87–88</t>
+  </si>
+  <si>
+    <t>89–90</t>
+  </si>
+  <si>
+    <t>92–93</t>
+  </si>
+  <si>
+    <t>96–97</t>
+  </si>
+  <si>
+    <t>98–99</t>
+  </si>
+  <si>
+    <t>+ Thought: 309ms</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>—</t>
   </si>
 </sst>
 </file>
@@ -1755,10 +1861,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E1" s="7"/>
     </row>
@@ -1770,10 +1876,10 @@
         <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E2" s="7"/>
     </row>
@@ -1785,10 +1891,10 @@
         <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E3" s="7"/>
     </row>
@@ -1797,13 +1903,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C4" t="s">
         <v>309</v>
       </c>
-      <c r="C4" t="s">
-        <v>310</v>
-      </c>
       <c r="D4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1811,13 +1917,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1825,13 +1931,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1839,13 +1945,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1853,13 +1959,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1867,13 +1973,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1881,13 +1987,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -1895,13 +2001,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -1909,13 +2015,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>324</v>
+      </c>
+      <c r="C12" t="s">
         <v>325</v>
       </c>
-      <c r="C12" t="s">
-        <v>326</v>
-      </c>
       <c r="D12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1923,13 +2029,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1937,13 +2043,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1951,13 +2057,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C15" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -1965,13 +2071,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C16" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -1982,10 +2088,10 @@
         <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -1996,10 +2102,10 @@
         <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -2010,10 +2116,10 @@
         <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -2021,13 +2127,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -2035,13 +2141,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C21" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -2049,13 +2155,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C22" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -2063,13 +2169,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C23" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -2077,13 +2183,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C24" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -2094,10 +2200,10 @@
         <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -2108,10 +2214,10 @@
         <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -2122,10 +2228,10 @@
         <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -2136,10 +2242,10 @@
         <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -2150,10 +2256,10 @@
         <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E29" s="9"/>
     </row>
@@ -2165,10 +2271,10 @@
         <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E30" s="11"/>
     </row>
@@ -2180,10 +2286,10 @@
         <v>110</v>
       </c>
       <c r="C31" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D31" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E31" s="11"/>
     </row>
@@ -2192,13 +2298,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>366</v>
+      </c>
+      <c r="C32" t="s">
         <v>367</v>
       </c>
-      <c r="C32" t="s">
-        <v>368</v>
-      </c>
       <c r="D32" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E32" s="11"/>
     </row>
@@ -2207,13 +2313,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C33" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D33" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E33" s="9"/>
     </row>
@@ -2222,13 +2328,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C34" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D34" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -2236,13 +2342,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C35" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D35" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -2250,13 +2356,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C36" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D36" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -2264,13 +2370,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C37" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D37" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -2278,13 +2384,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C38" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D38" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -2292,13 +2398,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C39" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D39" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -2306,13 +2412,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>377</v>
+      </c>
+      <c r="C40" t="s">
         <v>378</v>
       </c>
-      <c r="C40" t="s">
-        <v>379</v>
-      </c>
       <c r="D40" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -2320,13 +2426,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C41" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D41" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -2336,13 +2442,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C42" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D42" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -2350,13 +2456,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C43" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D43" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -2364,13 +2470,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C44" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
@@ -2378,13 +2484,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C45" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D45" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -2392,13 +2498,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C46" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D46" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -2406,13 +2512,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C47" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -2420,13 +2526,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C48" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D48" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
@@ -2434,13 +2540,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C49" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D49" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
@@ -2448,13 +2554,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C50" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D50" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
@@ -2462,13 +2568,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C51" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D51" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
@@ -2476,13 +2582,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C52" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D52" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
@@ -2490,13 +2596,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C53" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D53" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
@@ -2504,13 +2610,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C54" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D54" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
@@ -2518,13 +2624,13 @@
         <v>59</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
@@ -2532,13 +2638,13 @@
         <v>60</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
@@ -2546,13 +2652,13 @@
         <v>61</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="65" spans="5:11" x14ac:dyDescent="0.2">
@@ -2560,13 +2666,13 @@
         <v>62</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66" spans="5:11" x14ac:dyDescent="0.2">
@@ -2574,13 +2680,13 @@
         <v>66</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="70" spans="5:11" ht="24" x14ac:dyDescent="0.45">
@@ -2787,10 +2893,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -2798,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2" t="s">
         <v>234</v>
-      </c>
-      <c r="D2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -2812,13 +2918,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -2826,13 +2932,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -2843,10 +2949,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -2854,13 +2960,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" t="s">
         <v>255</v>
       </c>
-      <c r="C6" t="s">
-        <v>256</v>
-      </c>
       <c r="D6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -2868,13 +2974,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -2882,13 +2988,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -2899,10 +3005,10 @@
         <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -2910,13 +3016,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>290</v>
+      </c>
+      <c r="C10" t="s">
         <v>291</v>
       </c>
-      <c r="C10" t="s">
-        <v>292</v>
-      </c>
       <c r="D10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -2924,13 +3030,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -2938,13 +3044,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -2952,13 +3058,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>299</v>
+      </c>
+      <c r="C13" t="s">
         <v>300</v>
       </c>
-      <c r="C13" t="s">
-        <v>301</v>
-      </c>
       <c r="D13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -2966,13 +3072,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -2980,13 +3086,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -2997,10 +3103,10 @@
         <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -3008,13 +3114,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C17" t="s">
         <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -3022,13 +3128,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C18" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -3039,10 +3145,10 @@
         <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -3053,10 +3159,10 @@
         <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -3067,10 +3173,10 @@
         <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -3078,13 +3184,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -3092,13 +3198,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C23" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D23" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -3109,10 +3215,10 @@
         <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -3123,10 +3229,10 @@
         <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D25" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -3137,10 +3243,10 @@
         <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -3148,13 +3254,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C27" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3179,10 +3285,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -3190,13 +3296,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" t="s">
         <v>230</v>
       </c>
-      <c r="C2" t="s">
-        <v>231</v>
-      </c>
       <c r="D2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -3204,13 +3310,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3218,13 +3324,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -3232,13 +3338,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -3246,13 +3352,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -3260,13 +3366,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -3274,13 +3380,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -3291,10 +3397,10 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -3305,10 +3411,10 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -3319,10 +3425,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -3333,10 +3439,10 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -3347,10 +3453,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -3361,10 +3467,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -3375,10 +3481,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -3389,10 +3495,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -3400,13 +3506,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -3414,13 +3520,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -3428,13 +3534,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -3442,13 +3548,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -3456,13 +3562,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -3470,13 +3576,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>262</v>
+      </c>
+      <c r="C22" t="s">
         <v>263</v>
       </c>
-      <c r="C22" t="s">
-        <v>264</v>
-      </c>
       <c r="D22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -3484,13 +3590,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -3498,13 +3604,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -3512,13 +3618,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C25" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -3526,13 +3632,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -3540,13 +3646,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D27" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -3554,13 +3660,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C28" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -3568,13 +3674,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>271</v>
+      </c>
+      <c r="C29" t="s">
         <v>272</v>
       </c>
-      <c r="C29" t="s">
-        <v>273</v>
-      </c>
       <c r="D29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -3582,13 +3688,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D30" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -3596,13 +3702,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C31" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D31" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -3610,13 +3716,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C32" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -3624,13 +3730,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C33" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -3641,10 +3747,10 @@
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -3658,7 +3764,7 @@
         <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -3669,10 +3775,10 @@
         <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D36" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -3683,10 +3789,10 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D37" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -3697,10 +3803,10 @@
         <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -3711,10 +3817,10 @@
         <v>80</v>
       </c>
       <c r="C39" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -3725,10 +3831,10 @@
         <v>80</v>
       </c>
       <c r="C40" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -3739,10 +3845,10 @@
         <v>80</v>
       </c>
       <c r="C41" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -3753,10 +3859,10 @@
         <v>80</v>
       </c>
       <c r="C42" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D42" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -3770,7 +3876,7 @@
         <v>196</v>
       </c>
       <c r="D43" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -3781,10 +3887,10 @@
         <v>80</v>
       </c>
       <c r="C44" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -3795,10 +3901,10 @@
         <v>80</v>
       </c>
       <c r="C45" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D45" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -3806,13 +3912,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C46" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D46" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -3820,13 +3926,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C47" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -3834,13 +3940,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C48" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D48" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -3848,13 +3954,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C49" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D49" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -3862,13 +3968,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C50" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -3879,10 +3985,10 @@
         <v>104</v>
       </c>
       <c r="C51" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D51" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -3890,13 +3996,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>313</v>
+      </c>
+      <c r="C52" t="s">
         <v>314</v>
       </c>
-      <c r="C52" t="s">
-        <v>315</v>
-      </c>
       <c r="D52" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -3904,13 +4010,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C53" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D53" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -3918,13 +4024,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C54" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D54" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -3932,13 +4038,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C55" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D55" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -3946,13 +4052,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D56" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -3963,10 +4069,10 @@
         <v>92</v>
       </c>
       <c r="C57" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D57" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -3977,10 +4083,10 @@
         <v>92</v>
       </c>
       <c r="C58" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D58" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -3991,10 +4097,10 @@
         <v>92</v>
       </c>
       <c r="C59" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D59" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -4005,10 +4111,10 @@
         <v>92</v>
       </c>
       <c r="C60" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D60" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -4016,13 +4122,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>340</v>
+      </c>
+      <c r="C61" t="s">
         <v>341</v>
       </c>
-      <c r="C61" t="s">
-        <v>342</v>
-      </c>
       <c r="D61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -4030,13 +4136,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C62" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D62" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -4044,13 +4150,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C63" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D63" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -4058,13 +4164,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C64" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D64" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -4072,13 +4178,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>349</v>
+      </c>
+      <c r="C65" t="s">
         <v>350</v>
       </c>
-      <c r="C65" t="s">
-        <v>351</v>
-      </c>
       <c r="D65" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -4086,13 +4192,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D66" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -4100,13 +4206,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C67" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D67" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -4114,13 +4220,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C68" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D68" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -4128,13 +4234,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>372</v>
+      </c>
+      <c r="C69" t="s">
         <v>373</v>
       </c>
-      <c r="C69" t="s">
-        <v>374</v>
-      </c>
       <c r="D69" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -4158,13 +4264,13 @@
         <v>122</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4172,13 +4278,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C6" t="s">
         <v>230</v>
       </c>
-      <c r="C6" t="s">
-        <v>231</v>
-      </c>
       <c r="D6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4186,13 +4292,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4200,13 +4306,13 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" t="s">
         <v>234</v>
-      </c>
-      <c r="D8" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4214,13 +4320,13 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4228,13 +4334,13 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -4242,13 +4348,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -4256,13 +4362,13 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -4270,13 +4376,13 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -4284,13 +4390,13 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -4298,13 +4404,13 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -4315,10 +4421,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -4329,10 +4435,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -4343,10 +4449,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -4357,10 +4463,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -4371,10 +4477,10 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -4385,10 +4491,10 @@
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -4399,10 +4505,10 @@
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -4413,10 +4519,10 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
+        <v>249</v>
+      </c>
+      <c r="D23" t="s">
         <v>250</v>
-      </c>
-      <c r="D23" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -4427,10 +4533,10 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -4441,10 +4547,10 @@
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D25" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -4455,10 +4561,10 @@
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -4466,13 +4572,13 @@
         <v>22</v>
       </c>
       <c r="B27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C27" t="s">
         <v>255</v>
       </c>
-      <c r="C27" t="s">
-        <v>256</v>
-      </c>
       <c r="D27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -4480,13 +4586,13 @@
         <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -4494,13 +4600,13 @@
         <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C29" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D29" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -4508,13 +4614,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D30" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -4522,13 +4628,13 @@
         <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C31" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -4536,13 +4642,13 @@
         <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -4550,13 +4656,13 @@
         <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C33" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -4564,13 +4670,13 @@
         <v>29</v>
       </c>
       <c r="B34" t="s">
+        <v>262</v>
+      </c>
+      <c r="C34" t="s">
         <v>263</v>
       </c>
-      <c r="C34" t="s">
-        <v>264</v>
-      </c>
       <c r="D34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -4578,13 +4684,13 @@
         <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C35" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -4592,13 +4698,13 @@
         <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C36" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D36" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -4606,13 +4712,13 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C37" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D37" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -4620,13 +4726,13 @@
         <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -4634,13 +4740,13 @@
         <v>34</v>
       </c>
       <c r="B39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C39" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -4648,13 +4754,13 @@
         <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C40" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -4662,13 +4768,13 @@
         <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C41" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -4676,13 +4782,13 @@
         <v>37</v>
       </c>
       <c r="B42" t="s">
+        <v>271</v>
+      </c>
+      <c r="C42" t="s">
         <v>272</v>
       </c>
-      <c r="C42" t="s">
-        <v>273</v>
-      </c>
       <c r="D42" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -4690,13 +4796,13 @@
         <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C43" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D43" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -4704,13 +4810,13 @@
         <v>39</v>
       </c>
       <c r="B44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C44" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -4718,13 +4824,13 @@
         <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C45" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D45" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -4732,13 +4838,13 @@
         <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C46" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D46" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -4749,10 +4855,10 @@
         <v>35</v>
       </c>
       <c r="C47" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -4766,7 +4872,7 @@
         <v>48</v>
       </c>
       <c r="D48" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -4777,10 +4883,10 @@
         <v>35</v>
       </c>
       <c r="C49" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D49" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -4791,10 +4897,10 @@
         <v>35</v>
       </c>
       <c r="C50" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -4805,10 +4911,10 @@
         <v>35</v>
       </c>
       <c r="C51" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D51" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -4819,10 +4925,10 @@
         <v>35</v>
       </c>
       <c r="C52" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D52" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -4833,10 +4939,10 @@
         <v>80</v>
       </c>
       <c r="C53" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D53" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -4847,10 +4953,10 @@
         <v>80</v>
       </c>
       <c r="C54" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D54" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -4861,10 +4967,10 @@
         <v>80</v>
       </c>
       <c r="C55" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D55" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -4875,10 +4981,10 @@
         <v>80</v>
       </c>
       <c r="C56" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D56" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -4892,7 +4998,7 @@
         <v>196</v>
       </c>
       <c r="D57" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -4903,10 +5009,10 @@
         <v>80</v>
       </c>
       <c r="C58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D58" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -4917,10 +5023,10 @@
         <v>80</v>
       </c>
       <c r="C59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D59" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -4928,13 +5034,13 @@
         <v>55</v>
       </c>
       <c r="B60" t="s">
+        <v>290</v>
+      </c>
+      <c r="C60" t="s">
         <v>291</v>
       </c>
-      <c r="C60" t="s">
-        <v>292</v>
-      </c>
       <c r="D60" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -4942,13 +5048,13 @@
         <v>56</v>
       </c>
       <c r="B61" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C61" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D61" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -4956,13 +5062,13 @@
         <v>57</v>
       </c>
       <c r="B62" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C62" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D62" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -4970,13 +5076,13 @@
         <v>58</v>
       </c>
       <c r="B63" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C63" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D63" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -4984,13 +5090,13 @@
         <v>59</v>
       </c>
       <c r="B64" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C64" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D64" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -4998,13 +5104,13 @@
         <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C65" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D65" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -5012,13 +5118,13 @@
         <v>61</v>
       </c>
       <c r="B66" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C66" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D66" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -5026,13 +5132,13 @@
         <v>62</v>
       </c>
       <c r="B67" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C67" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D67" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -5040,13 +5146,13 @@
         <v>63</v>
       </c>
       <c r="B68" t="s">
+        <v>299</v>
+      </c>
+      <c r="C68" t="s">
         <v>300</v>
       </c>
-      <c r="C68" t="s">
-        <v>301</v>
-      </c>
       <c r="D68" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -5054,13 +5160,13 @@
         <v>64</v>
       </c>
       <c r="B69" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C69" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D69" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
@@ -5068,13 +5174,13 @@
         <v>65</v>
       </c>
       <c r="B70" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C70" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D70" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
@@ -5082,13 +5188,13 @@
         <v>66</v>
       </c>
       <c r="B71" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C71" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D71" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -5099,10 +5205,10 @@
         <v>104</v>
       </c>
       <c r="C72" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D72" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
@@ -5113,10 +5219,10 @@
         <v>104</v>
       </c>
       <c r="C73" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D73" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
@@ -5127,10 +5233,10 @@
         <v>104</v>
       </c>
       <c r="C74" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D74" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
@@ -5141,10 +5247,10 @@
         <v>104</v>
       </c>
       <c r="C75" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D75" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
@@ -5152,13 +5258,13 @@
         <v>71</v>
       </c>
       <c r="B76" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C76" t="s">
         <v>107</v>
       </c>
       <c r="D76" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
@@ -5166,13 +5272,13 @@
         <v>72</v>
       </c>
       <c r="B77" t="s">
+        <v>308</v>
+      </c>
+      <c r="C77" t="s">
         <v>309</v>
       </c>
-      <c r="C77" t="s">
-        <v>310</v>
-      </c>
       <c r="D77" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
@@ -5180,13 +5286,13 @@
         <v>73</v>
       </c>
       <c r="B78" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C78" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D78" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
@@ -5194,13 +5300,13 @@
         <v>74</v>
       </c>
       <c r="B79" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C79" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D79" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
@@ -5208,13 +5314,13 @@
         <v>75</v>
       </c>
       <c r="B80" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D80" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
@@ -5222,13 +5328,13 @@
         <v>76</v>
       </c>
       <c r="B81" t="s">
+        <v>313</v>
+      </c>
+      <c r="C81" t="s">
         <v>314</v>
       </c>
-      <c r="C81" t="s">
-        <v>315</v>
-      </c>
       <c r="D81" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
@@ -5236,13 +5342,13 @@
         <v>77</v>
       </c>
       <c r="B82" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C82" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D82" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
@@ -5250,13 +5356,13 @@
         <v>78</v>
       </c>
       <c r="B83" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C83" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D83" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
@@ -5264,13 +5370,13 @@
         <v>79</v>
       </c>
       <c r="B84" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C84" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D84" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
@@ -5278,13 +5384,13 @@
         <v>80</v>
       </c>
       <c r="B85" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C85" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D85" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
@@ -5292,13 +5398,13 @@
         <v>81</v>
       </c>
       <c r="B86" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C86" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D86" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
@@ -5306,13 +5412,13 @@
         <v>82</v>
       </c>
       <c r="B87" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C87" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D87" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
@@ -5320,13 +5426,13 @@
         <v>83</v>
       </c>
       <c r="B88" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C88" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D88" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
@@ -5334,13 +5440,13 @@
         <v>84</v>
       </c>
       <c r="B89" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C89" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D89" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
@@ -5348,13 +5454,13 @@
         <v>85</v>
       </c>
       <c r="B90" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C90" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D90" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
@@ -5362,13 +5468,13 @@
         <v>86</v>
       </c>
       <c r="B91" t="s">
+        <v>324</v>
+      </c>
+      <c r="C91" t="s">
         <v>325</v>
       </c>
-      <c r="C91" t="s">
-        <v>326</v>
-      </c>
       <c r="D91" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
@@ -5376,13 +5482,13 @@
         <v>87</v>
       </c>
       <c r="B92" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C92" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D92" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
@@ -5390,13 +5496,13 @@
         <v>88</v>
       </c>
       <c r="B93" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C93" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D93" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
@@ -5404,13 +5510,13 @@
         <v>89</v>
       </c>
       <c r="B94" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C94" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D94" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
@@ -5418,13 +5524,13 @@
         <v>90</v>
       </c>
       <c r="B95" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C95" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D95" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
@@ -5435,10 +5541,10 @@
         <v>92</v>
       </c>
       <c r="C96" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D96" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
@@ -5449,10 +5555,10 @@
         <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D97" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
@@ -5463,10 +5569,10 @@
         <v>92</v>
       </c>
       <c r="C98" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D98" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
@@ -5477,10 +5583,10 @@
         <v>92</v>
       </c>
       <c r="C99" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D99" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
@@ -5491,10 +5597,10 @@
         <v>92</v>
       </c>
       <c r="C100" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
@@ -5505,10 +5611,10 @@
         <v>92</v>
       </c>
       <c r="C101" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D101" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
@@ -5519,10 +5625,10 @@
         <v>92</v>
       </c>
       <c r="C102" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D102" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
@@ -5533,10 +5639,10 @@
         <v>92</v>
       </c>
       <c r="C103" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D103" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
@@ -5547,10 +5653,10 @@
         <v>92</v>
       </c>
       <c r="C104" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D104" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
@@ -5561,10 +5667,10 @@
         <v>92</v>
       </c>
       <c r="C105" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D105" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
@@ -5572,13 +5678,13 @@
         <v>101</v>
       </c>
       <c r="B106" t="s">
+        <v>340</v>
+      </c>
+      <c r="C106" t="s">
         <v>341</v>
       </c>
-      <c r="C106" t="s">
-        <v>342</v>
-      </c>
       <c r="D106" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
@@ -5586,13 +5692,13 @@
         <v>102</v>
       </c>
       <c r="B107" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C107" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D107" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
@@ -5600,13 +5706,13 @@
         <v>103</v>
       </c>
       <c r="B108" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C108" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D108" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
@@ -5614,13 +5720,13 @@
         <v>104</v>
       </c>
       <c r="B109" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C109" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D109" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
@@ -5628,13 +5734,13 @@
         <v>105</v>
       </c>
       <c r="B110" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C110" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D110" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
@@ -5642,13 +5748,13 @@
         <v>106</v>
       </c>
       <c r="B111" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C111" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D111" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
@@ -5656,13 +5762,13 @@
         <v>107</v>
       </c>
       <c r="B112" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C112" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D112" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
@@ -5670,13 +5776,13 @@
         <v>108</v>
       </c>
       <c r="B113" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C113" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D113" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
@@ -5684,13 +5790,13 @@
         <v>109</v>
       </c>
       <c r="B114" t="s">
+        <v>349</v>
+      </c>
+      <c r="C114" t="s">
         <v>350</v>
       </c>
-      <c r="C114" t="s">
-        <v>351</v>
-      </c>
       <c r="D114" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
@@ -5698,13 +5804,13 @@
         <v>110</v>
       </c>
       <c r="B115" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C115" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
@@ -5712,13 +5818,13 @@
         <v>111</v>
       </c>
       <c r="B116" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C116" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D116" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
@@ -5726,13 +5832,13 @@
         <v>112</v>
       </c>
       <c r="B117" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C117" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D117" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
@@ -5740,13 +5846,13 @@
         <v>113</v>
       </c>
       <c r="B118" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C118" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D118" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
@@ -5754,13 +5860,13 @@
         <v>114</v>
       </c>
       <c r="B119" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C119" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D119" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
@@ -5768,13 +5874,13 @@
         <v>115</v>
       </c>
       <c r="B120" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C120" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D120" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
@@ -5785,10 +5891,10 @@
         <v>97</v>
       </c>
       <c r="C121" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D121" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
@@ -5799,10 +5905,10 @@
         <v>97</v>
       </c>
       <c r="C122" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D122" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
@@ -5813,10 +5919,10 @@
         <v>97</v>
       </c>
       <c r="C123" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D123" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
@@ -5827,10 +5933,10 @@
         <v>97</v>
       </c>
       <c r="C124" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D124" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
@@ -5841,10 +5947,10 @@
         <v>97</v>
       </c>
       <c r="C125" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D125" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
@@ -5855,10 +5961,10 @@
         <v>110</v>
       </c>
       <c r="C126" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D126" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
@@ -5869,10 +5975,10 @@
         <v>110</v>
       </c>
       <c r="C127" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D127" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
@@ -5883,10 +5989,10 @@
         <v>110</v>
       </c>
       <c r="C128" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D128" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
@@ -5897,10 +6003,10 @@
         <v>110</v>
       </c>
       <c r="C129" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D129" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
@@ -5911,10 +6017,10 @@
         <v>110</v>
       </c>
       <c r="C130" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D130" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
@@ -5922,13 +6028,13 @@
         <v>126</v>
       </c>
       <c r="B131" t="s">
+        <v>366</v>
+      </c>
+      <c r="C131" t="s">
         <v>367</v>
       </c>
-      <c r="C131" t="s">
-        <v>368</v>
-      </c>
       <c r="D131" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
@@ -5936,13 +6042,13 @@
         <v>127</v>
       </c>
       <c r="B132" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C132" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D132" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
@@ -5950,13 +6056,13 @@
         <v>128</v>
       </c>
       <c r="B133" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C133" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D133" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
@@ -5964,13 +6070,13 @@
         <v>129</v>
       </c>
       <c r="B134" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C134" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D134" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
@@ -5978,13 +6084,13 @@
         <v>130</v>
       </c>
       <c r="B135" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C135" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D135" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
@@ -5992,13 +6098,13 @@
         <v>131</v>
       </c>
       <c r="B136" t="s">
+        <v>372</v>
+      </c>
+      <c r="C136" t="s">
         <v>373</v>
       </c>
-      <c r="C136" t="s">
-        <v>374</v>
-      </c>
       <c r="D136" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
@@ -6006,13 +6112,13 @@
         <v>132</v>
       </c>
       <c r="B137" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C137" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D137" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
@@ -6020,13 +6126,13 @@
         <v>133</v>
       </c>
       <c r="B138" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C138" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D138" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
@@ -6034,13 +6140,13 @@
         <v>134</v>
       </c>
       <c r="B139" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C139" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D139" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
@@ -6048,13 +6154,13 @@
         <v>135</v>
       </c>
       <c r="B140" t="s">
+        <v>377</v>
+      </c>
+      <c r="C140" t="s">
         <v>378</v>
       </c>
-      <c r="C140" t="s">
-        <v>379</v>
-      </c>
       <c r="D140" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
@@ -6062,13 +6168,13 @@
         <v>136</v>
       </c>
       <c r="B141" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C141" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D141" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
@@ -6076,13 +6182,13 @@
         <v>137</v>
       </c>
       <c r="B142" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C142" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D142" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
@@ -6090,13 +6196,13 @@
         <v>138</v>
       </c>
       <c r="B143" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C143" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D143" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
@@ -6104,13 +6210,13 @@
         <v>139</v>
       </c>
       <c r="B144" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C144" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D144" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
@@ -6118,13 +6224,13 @@
         <v>140</v>
       </c>
       <c r="B145" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C145" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D145" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
@@ -6132,13 +6238,13 @@
         <v>141</v>
       </c>
       <c r="B146" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C146" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D146" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
@@ -6146,13 +6252,13 @@
         <v>142</v>
       </c>
       <c r="B147" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C147" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D147" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
@@ -6160,13 +6266,13 @@
         <v>143</v>
       </c>
       <c r="B148" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C148" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D148" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
@@ -6174,13 +6280,13 @@
         <v>144</v>
       </c>
       <c r="B149" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C149" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D149" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
@@ -6188,13 +6294,13 @@
         <v>145</v>
       </c>
       <c r="B150" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C150" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D150" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
@@ -6202,13 +6308,13 @@
         <v>146</v>
       </c>
       <c r="B151" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C151" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D151" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
@@ -6216,13 +6322,13 @@
         <v>147</v>
       </c>
       <c r="B152" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C152" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D152" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
@@ -6230,13 +6336,13 @@
         <v>148</v>
       </c>
       <c r="B153" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C153" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D153" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
@@ -6244,13 +6350,13 @@
         <v>149</v>
       </c>
       <c r="B154" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C154" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D154" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
@@ -6258,13 +6364,13 @@
         <v>150</v>
       </c>
       <c r="B155" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C155" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D155" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -6273,6 +6379,1275 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A30476-851E-3243-90F4-BEEDEC44EC1C}">
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="38" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" customWidth="1"/>
+    <col min="7" max="7" width="24.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>201</v>
+      </c>
+      <c r="F3" t="s">
+        <v>409</v>
+      </c>
+      <c r="G3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>200</v>
+      </c>
+      <c r="F4" t="s">
+        <v>409</v>
+      </c>
+      <c r="G4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>200</v>
+      </c>
+      <c r="F5" t="s">
+        <v>409</v>
+      </c>
+      <c r="G5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>200</v>
+      </c>
+      <c r="F6" t="s">
+        <v>409</v>
+      </c>
+      <c r="G6" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>200</v>
+      </c>
+      <c r="F7" t="s">
+        <v>409</v>
+      </c>
+      <c r="G7" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>200</v>
+      </c>
+      <c r="F8" t="s">
+        <v>409</v>
+      </c>
+      <c r="G8" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>200</v>
+      </c>
+      <c r="F9" t="s">
+        <v>409</v>
+      </c>
+      <c r="G9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10">
+        <v>200</v>
+      </c>
+      <c r="F10" t="s">
+        <v>409</v>
+      </c>
+      <c r="G10" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11">
+        <v>200</v>
+      </c>
+      <c r="F11" t="s">
+        <v>409</v>
+      </c>
+      <c r="G11" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12">
+        <v>200</v>
+      </c>
+      <c r="F12" t="s">
+        <v>409</v>
+      </c>
+      <c r="G12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E13">
+        <v>200</v>
+      </c>
+      <c r="F13" t="s">
+        <v>409</v>
+      </c>
+      <c r="G13" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E14">
+        <v>200</v>
+      </c>
+      <c r="F14" t="s">
+        <v>409</v>
+      </c>
+      <c r="G14" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E15">
+        <v>200</v>
+      </c>
+      <c r="F15" t="s">
+        <v>409</v>
+      </c>
+      <c r="G15" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16">
+        <v>200</v>
+      </c>
+      <c r="F16" t="s">
+        <v>409</v>
+      </c>
+      <c r="G16" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17">
+        <v>201</v>
+      </c>
+      <c r="F17" t="s">
+        <v>409</v>
+      </c>
+      <c r="G17" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>411</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>412</v>
+      </c>
+      <c r="F18" t="s">
+        <v>410</v>
+      </c>
+      <c r="G18" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19">
+        <v>200</v>
+      </c>
+      <c r="F19" t="s">
+        <v>409</v>
+      </c>
+      <c r="G19" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>413</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>412</v>
+      </c>
+      <c r="F20" t="s">
+        <v>410</v>
+      </c>
+      <c r="G20" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>414</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>172</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>412</v>
+      </c>
+      <c r="F21" t="s">
+        <v>410</v>
+      </c>
+      <c r="G21" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>415</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" t="s">
+        <v>412</v>
+      </c>
+      <c r="F22" t="s">
+        <v>409</v>
+      </c>
+      <c r="G22" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>416</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>172</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" t="s">
+        <v>412</v>
+      </c>
+      <c r="F23" t="s">
+        <v>409</v>
+      </c>
+      <c r="G23" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E24" t="s">
+        <v>412</v>
+      </c>
+      <c r="F24" t="s">
+        <v>409</v>
+      </c>
+      <c r="G24" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>45</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E25" t="s">
+        <v>412</v>
+      </c>
+      <c r="F25" t="s">
+        <v>409</v>
+      </c>
+      <c r="G25" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>417</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" t="s">
+        <v>412</v>
+      </c>
+      <c r="F26" t="s">
+        <v>409</v>
+      </c>
+      <c r="G26" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" t="s">
+        <v>170</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E27" t="s">
+        <v>412</v>
+      </c>
+      <c r="F27" t="s">
+        <v>409</v>
+      </c>
+      <c r="G27" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>61</v>
+      </c>
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" t="s">
+        <v>170</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" t="s">
+        <v>412</v>
+      </c>
+      <c r="F28" t="s">
+        <v>409</v>
+      </c>
+      <c r="G28" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>62</v>
+      </c>
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" t="s">
+        <v>170</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" t="s">
+        <v>412</v>
+      </c>
+      <c r="F29" t="s">
+        <v>409</v>
+      </c>
+      <c r="G29" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>63</v>
+      </c>
+      <c r="B30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" t="s">
+        <v>170</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" t="s">
+        <v>412</v>
+      </c>
+      <c r="F30" t="s">
+        <v>409</v>
+      </c>
+      <c r="G30" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>418</v>
+      </c>
+      <c r="B31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E31" t="s">
+        <v>412</v>
+      </c>
+      <c r="F31" t="s">
+        <v>409</v>
+      </c>
+      <c r="G31" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>73</v>
+      </c>
+      <c r="B32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" t="s">
+        <v>170</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E32" t="s">
+        <v>412</v>
+      </c>
+      <c r="F32" t="s">
+        <v>409</v>
+      </c>
+      <c r="G32" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>419</v>
+      </c>
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" t="s">
+        <v>170</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E33" t="s">
+        <v>412</v>
+      </c>
+      <c r="F33" t="s">
+        <v>409</v>
+      </c>
+      <c r="G33" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>78</v>
+      </c>
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" t="s">
+        <v>412</v>
+      </c>
+      <c r="F34" t="s">
+        <v>409</v>
+      </c>
+      <c r="G34" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>79</v>
+      </c>
+      <c r="B35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" t="s">
+        <v>170</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E35" t="s">
+        <v>412</v>
+      </c>
+      <c r="F35" t="s">
+        <v>409</v>
+      </c>
+      <c r="G35" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>420</v>
+      </c>
+      <c r="B36" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" t="s">
+        <v>170</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" t="s">
+        <v>412</v>
+      </c>
+      <c r="F36" t="s">
+        <v>409</v>
+      </c>
+      <c r="G36" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>421</v>
+      </c>
+      <c r="B37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" t="s">
+        <v>170</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E37" t="s">
+        <v>412</v>
+      </c>
+      <c r="F37" t="s">
+        <v>409</v>
+      </c>
+      <c r="G37" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" t="s">
+        <v>170</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" t="s">
+        <v>412</v>
+      </c>
+      <c r="F38" t="s">
+        <v>409</v>
+      </c>
+      <c r="G38" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>85</v>
+      </c>
+      <c r="B39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E39" t="s">
+        <v>412</v>
+      </c>
+      <c r="F39" t="s">
+        <v>409</v>
+      </c>
+      <c r="G39" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>86</v>
+      </c>
+      <c r="B40" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" t="s">
+        <v>170</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" t="s">
+        <v>412</v>
+      </c>
+      <c r="F40" t="s">
+        <v>409</v>
+      </c>
+      <c r="G40" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>422</v>
+      </c>
+      <c r="B41" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" t="s">
+        <v>170</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E41" t="s">
+        <v>412</v>
+      </c>
+      <c r="F41" t="s">
+        <v>409</v>
+      </c>
+      <c r="G41" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>423</v>
+      </c>
+      <c r="B42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" t="s">
+        <v>170</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E42" t="s">
+        <v>412</v>
+      </c>
+      <c r="F42" t="s">
+        <v>409</v>
+      </c>
+      <c r="G42" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>91</v>
+      </c>
+      <c r="B43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" t="s">
+        <v>170</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E43" t="s">
+        <v>412</v>
+      </c>
+      <c r="F43" t="s">
+        <v>409</v>
+      </c>
+      <c r="G43" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>424</v>
+      </c>
+      <c r="B44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E44" t="s">
+        <v>412</v>
+      </c>
+      <c r="F44" t="s">
+        <v>409</v>
+      </c>
+      <c r="G44" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>94</v>
+      </c>
+      <c r="B45" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E45" t="s">
+        <v>412</v>
+      </c>
+      <c r="F45" t="s">
+        <v>409</v>
+      </c>
+      <c r="G45" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>95</v>
+      </c>
+      <c r="B46" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" t="s">
+        <v>170</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E46" t="s">
+        <v>412</v>
+      </c>
+      <c r="F46" t="s">
+        <v>409</v>
+      </c>
+      <c r="G46" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>425</v>
+      </c>
+      <c r="B47" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E47" t="s">
+        <v>412</v>
+      </c>
+      <c r="F47" t="s">
+        <v>409</v>
+      </c>
+      <c r="G47" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>426</v>
+      </c>
+      <c r="B48" t="s">
+        <v>107</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E48">
+        <v>200</v>
+      </c>
+      <c r="F48" t="s">
+        <v>409</v>
+      </c>
+      <c r="G48" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>100</v>
+      </c>
+      <c r="B49" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" t="s">
+        <v>170</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E49" t="s">
+        <v>412</v>
+      </c>
+      <c r="F49" t="s">
+        <v>409</v>
+      </c>
+      <c r="G49" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>101</v>
+      </c>
+      <c r="B50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E50">
+        <v>200</v>
+      </c>
+      <c r="F50" t="s">
+        <v>409</v>
+      </c>
+      <c r="G50" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>102</v>
+      </c>
+      <c r="B51" t="s">
+        <v>112</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E51">
+        <v>200</v>
+      </c>
+      <c r="F51" t="s">
+        <v>409</v>
+      </c>
+      <c r="G51" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>103</v>
+      </c>
+      <c r="B52" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52" t="s">
+        <v>192</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E52" t="s">
+        <v>412</v>
+      </c>
+      <c r="F52" t="s">
+        <v>408</v>
+      </c>
+      <c r="G52" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>104</v>
+      </c>
+      <c r="B53" t="s">
+        <v>115</v>
+      </c>
+      <c r="C53" t="s">
+        <v>192</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E53" t="s">
+        <v>412</v>
+      </c>
+      <c r="F53" t="s">
+        <v>408</v>
+      </c>
+      <c r="G53" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>105</v>
+      </c>
+      <c r="B54" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E54">
+        <v>200</v>
+      </c>
+      <c r="F54" t="s">
+        <v>409</v>
+      </c>
+      <c r="G54" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>106</v>
+      </c>
+      <c r="B55" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E55">
+        <v>200</v>
+      </c>
+      <c r="F55" t="s">
+        <v>409</v>
+      </c>
+      <c r="G55" t="s">
+        <v>396</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B34B6C3-5226-6B42-88BE-FE926E2C599F}">
   <dimension ref="A1:Q120"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -6333,7 +7708,7 @@
         <v>222</v>
       </c>
       <c r="G2" t="s">
-        <v>227</v>
+        <v>395</v>
       </c>
       <c r="H2" t="s">
         <v>128</v>
@@ -6358,6 +7733,9 @@
       <c r="F3" t="s">
         <v>224</v>
       </c>
+      <c r="G3" t="s">
+        <v>223</v>
+      </c>
       <c r="H3" t="s">
         <v>129</v>
       </c>
@@ -6425,7 +7803,7 @@
         <v>216</v>
       </c>
       <c r="F6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H6" t="s">
         <v>132</v>
@@ -8638,7 +10016,10 @@
         <v>220</v>
       </c>
       <c r="F102" t="s">
-        <v>224</v>
+        <v>222</v>
+      </c>
+      <c r="G102" t="s">
+        <v>394</v>
       </c>
       <c r="H102" t="s">
         <v>207</v>
@@ -8661,7 +10042,10 @@
         <v>220</v>
       </c>
       <c r="F103" t="s">
-        <v>224</v>
+        <v>222</v>
+      </c>
+      <c r="G103" t="s">
+        <v>394</v>
       </c>
       <c r="H103" t="s">
         <v>208</v>
@@ -8684,7 +10068,10 @@
         <v>219</v>
       </c>
       <c r="F104" t="s">
-        <v>224</v>
+        <v>222</v>
+      </c>
+      <c r="G104" t="s">
+        <v>226</v>
       </c>
       <c r="H104" t="s">
         <v>209</v>
@@ -8707,7 +10094,10 @@
         <v>219</v>
       </c>
       <c r="F105" t="s">
-        <v>224</v>
+        <v>222</v>
+      </c>
+      <c r="G105" t="s">
+        <v>226</v>
       </c>
       <c r="H105" t="s">
         <v>210</v>
@@ -8730,7 +10120,10 @@
         <v>216</v>
       </c>
       <c r="F106" t="s">
-        <v>224</v>
+        <v>222</v>
+      </c>
+      <c r="G106" t="s">
+        <v>223</v>
       </c>
       <c r="H106" t="s">
         <v>211</v>
@@ -8756,7 +10149,7 @@
         <v>222</v>
       </c>
       <c r="G107" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H107" t="s">
         <v>212</v>
